--- a/public/templates/teacher_import_template.xlsx
+++ b/public/templates/teacher_import_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
   <si>
     <r>
       <rPr>
@@ -39,7 +39,7 @@
         <color rgb="FFFFFFFF"/>
         <sz val="11"/>
       </rPr>
-      <t xml:space="preserve">Name
+      <t xml:space="preserve">Teacher/Adviser Name
 </t>
     </r>
     <r>
@@ -125,6 +125,25 @@
         <sz val="9"/>
       </rPr>
       <t>(09XXXXXXXXX)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">Email
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="9"/>
+      </rPr>
+      <t>(optional)</t>
     </r>
   </si>
   <si>
@@ -726,18 +745,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="40" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,6 +775,9 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25"/>
@@ -884,464 +907,464 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
       <c r="G1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/teacher_import_template.xlsx
+++ b/public/templates/teacher_import_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <r>
       <rPr>
@@ -162,6 +162,9 @@
     <t>7</t>
   </si>
   <si>
+    <t>Male</t>
+  </si>
+  <si>
     <t>Banag Elementary School</t>
   </si>
   <si>
@@ -175,6 +178,9 @@
   </si>
   <si>
     <t>8</t>
+  </si>
+  <si>
+    <t>Female</t>
   </si>
   <si>
     <t>Barangay V Elementary School</t>
@@ -902,10 +908,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -927,216 +933,222 @@
       <c r="G1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
       <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
       <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
       <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1144,227 +1156,227 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/teacher_import_template.xlsx
+++ b/public/templates/teacher_import_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="76">
   <si>
     <r>
       <rPr>
@@ -895,10 +895,10 @@
       <formula1>Dropdowns!$A$1:$A$45</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Select Grade" prompt="Choose from the list" sqref="D10:D101">
-      <formula1>Dropdowns!$B$1:$B$12</formula1>
+      <formula1>Dropdowns!$B$1:$B$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Select Grade" prompt="Choose from the list" sqref="D2:D101">
-      <formula1>Dropdowns!$B$1:$B$12</formula1>
+      <formula1>Dropdowns!$B$1:$B$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1127,9 +1127,6 @@
       <c r="A11" t="s">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
       <c r="D11" t="s">
         <v>51</v>
       </c>
@@ -1140,9 +1137,6 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>

--- a/public/templates/teacher_import_template.xlsx
+++ b/public/templates/teacher_import_template.xlsx
@@ -407,8 +407,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -754,138 +758,438 @@
   <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="6" max="6" width="22" style="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="F76" s="1"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="F77" s="1"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="F78" s="1"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1"/>
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="F96" s="1"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="F98" s="1"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+      <c r="F101" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Select School" prompt="Choose from the list" sqref="C10:C101">

--- a/public/templates/teacher_import_template.xlsx
+++ b/public/templates/teacher_import_template.xlsx
@@ -134,7 +134,7 @@
         <color rgb="FFFFFFFF"/>
         <sz val="11"/>
       </rPr>
-      <t xml:space="preserve">Email
+      <t xml:space="preserve">Email/DepEd Email
 </t>
     </r>
     <r>
@@ -143,7 +143,7 @@
         <color rgb="FFFFFFFF"/>
         <sz val="9"/>
       </rPr>
-      <t>(optional)</t>
+      <t>(required)</t>
     </r>
   </si>
   <si>
